--- a/results/foodmood_50_du_doan_moi.xlsx
+++ b/results/foodmood_50_du_doan_moi.xlsx
@@ -714,7 +714,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Không nhắc rõ</t>
+          <t>Hài lòng</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Không hài lòng</t>
+          <t>Không nhắc rõ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Không nhắc rõ</t>
+          <t>Không hài lòng</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Hài lòng</t>
+          <t>Không nhắc rõ</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hài lòng</t>
+          <t>Không nhắc rõ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Hài lòng</t>
+          <t>Không nhắc rõ</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Không hài lòng</t>
+          <t>Không nhắc rõ</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Không nhắc rõ</t>
+          <t>Hài lòng</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Hài lòng</t>
+          <t>Không nhắc rõ</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Không hài lòng</t>
+          <t>Không nhắc rõ</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Không hài lòng</t>
+          <t>Hài lòng</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Trung lập</t>
+          <t>Không hài lòng</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Trung lập</t>
+          <t>Không nhắc rõ</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Lẫn lộn</t>
+          <t>Hài lòng</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Không nhắc rõ</t>
+          <t>Hài lòng</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Trung lập</t>
+          <t>Không nhắc rõ</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Không hài lòng</t>
+          <t>Không nhắc rõ</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Không nhắc rõ</t>
+          <t>Hài lòng</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hài lòng</t>
+          <t>Không nhắc rõ</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Trung lập</t>
+          <t>Không nhắc rõ</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
